--- a/summarization/revisao_topicos.xlsx
+++ b/summarization/revisao_topicos.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Problemas de Afastamento e Perícia em SIAPENET</t>
+          <t>Problemas de Afastamentos e Atestados no Sistema de RH</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -570,12 +570,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas no sistema de afastamento e atestados, incluindo erros ao lançar afastamentos, impossibilidade de agendar perícia, inconsistências em registros de funcionários, problemas com a validade de documentos e dificuldades para incluir atestados. Além disso, há também relatos de problemas com o sistema SIAPENET, como impossibilidade de acessar informações e erros ao tentar realizar login. Os usuários relatam que esses problemas afetam unidades de diferentes órgãos e se manifestam tanto em perícia agendadas incorretamente quanto em perícia antigas que deveriam ter sido encerradas mas permaneceram abertas no sistema.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o sistema de afastamentos e atestados, incluindo erros ao tentar lançar ou registrar afastamentos, inconsistências em registros de funcionários, problemas de integração entre sistemas e dificuldades para agendar perícias. Além disso, há também mencionadas falhas na validação de documentos e assinaturas digitais. Os usuários relatam que os erros persistem mesmo após tentativas de resolver o problema, o que causa atrasos nos processos e impacta negativamente no trabalho dos funcionários.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>O problema do sistema SIAPENET está impedindo a realização de afastamentos, perícia e atestados, causando transtornos para os usuários e operadores.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento. Além disso, os erros persistem mesmo após tentativas de resolver o problema, causando transtornos aos funcionários e impactando negativamente no trabalho dos gestores.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Problemas de Adicionais Ocupacionais em SIAPENET</t>
+          <t>Dificuldades com Adicionais Ocupacionais no SIAPenet</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -599,16 +599,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante é a dificuldade de inclusão e gerenciamento de adicionais ocupacionais, especialmente os relacionados à insalubridade e periculosidade. Os usuários relatam problemas ao tentar cadastrar, incluir ou excluir esses adicionais no sistema SIAPENET, o que afeta a geração de portarias e o pagamento dos benefícios. Alguns casos mencionam alterações em unidades orgânicas (UORGs), migrações de UORGs e problemas com a localização e gerenciamento de laudos. A falta de orientação e suporte técnico é frequentemente citada como um problema adicional.</t>
+          <t>O padrão dominante neste cluster é a dificuldade de inclusão ou manutenção de adicionais ocupacionais, especialmente os relacionados à insalubridade e periculosidade, em sistemas como o SIAPenet. Isso se manifesta em problemas de localização de unidades orgânicas (UORG), gerar portarias de concessão, inclusão de novos laudos e erros de pagamento. Além disso, há também questões relacionadas à migração de UORGs, alteração de percentuais de insalubridade e problemas de sincronização entre sistemas.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>O bloqueio ou dificuldade na inclusão de adicionais ocupacionais pode levar à falta de pagamento dos benefícios, afetando os funcionários que dependem desses adicionais. Além disso, a ineficiência no gerenciamento desses adicionais pode causar problemas administrativos e financeiros para as unidades orgânicas envolvidas.
-Observações:
-- A frequência e urgência dos tickets sugerem que o problema é recorrente e causa desconforto significativo aos usuários.
-- A diversidade de casos apresentados indica que o problema não se limita a uma única situação ou contexto, mas sim é um desafio mais amplo no gerenciamento de adicionais ocupacioniais no SIAPENET.
-- A necessidade de orientação e suporte técnico é frequentemente mencionada, sugerindo que há uma lacuna na documentação ou treinamento disponível para os usuários.</t>
+          <t>As unidades precisam lançar adicionais ocupacionais manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento. Além disso, os erros de pagamento podem levar a descontos indevidos ou falta de pagamento de adicionais ocupacionais, afetando negativamente os funcionários que os merecem.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -624,7 +620,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Problemas de Atestados Pendentes em SIAPENET</t>
+          <t>Problemas de Integração entre SIAPENET e Módulos Governamentais</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -632,13 +628,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é o problema de "atestados pendentes" em diferentes órgãos e unidades, como SIASS, FUNASA, INSS, SIAPECAD, entre outros. Os usuários relatam que possuem atestados pendentes da mesma espécie, com data de afastamento anterior, mas não conseguem realizar a retirada ou análise desses documentos. Alguns casos mencionam erros no sistema web SIAPENET, enquanto outros apontam para atrasos na vinculação integrada e falta de atualização dos dados.</t>
+          <t>O padrão dominante é o problema de integração entre sistemas, especificamente com a SIAPENET e outros módulos do governo federal. Os usuários possuem atestados pendentes ou não encontram os registros anteriores em diferentes unidades ou órgãos, como INSS, FUNASA, SIAPECAD, etc. Isso causa atraso na situação dos afastamentos e necessidade de intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>A presença de atestados pendentes impede o funcionamento normal das unidades, acumulando filas de espera sem solução sistêmica disponível. Isso afeta não apenas os usuários que aguardam a resolução desses problemas, mas também as equipes responsáveis por gerenciar esses processos, que precisam lidar com a burocracia e a falta de informações atualizadas.
-Nota: A frequência e urgência desse problema podem ser inferidas pela grande quantidade de tickets semelhantes (20) e pelo tom dos relatos, que indicam frustração e necessidade de resolução imediata.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -654,7 +649,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Problemas de Acesso e Agendamento em SIAPENET</t>
+          <t>Falhas na Sincronização entre SIAPE e SIASS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -662,12 +657,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante é o problema de acesso e agendamento de perícias médicas no sistema, incluindo a impossibilidade de realizar perícias presenciais em casos específicos, como quando o perito está afastado ou não tem acesso ao prontuário do paciente. Além disso, há problemas com a homologação de atestados e a possibilidade de agendar perícias sem que os profissionais tenham acesso aos prontuários completos. O sistema também apresenta problemas de compatibilidade entre as unidades e os sistemas utilizados.</t>
+          <t>A falha na integração entre o SIAPE e SIASS impede que os afastamentos registrados em um sistema sejam refletidos automaticamente no outro. O problema se manifesta tanto em afastamentos recentes quanto em registros antigos que já deveriam ter sido sincronizados. Quando o servidor muda de lotação, o histórico de afastamentos do órgão anterior fica inacessível para a nova unidade, exigindo intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>A falta de acesso a perícias médicas presenciais e o problema de agendamento afetam negativamente a capacidade dos servidores de realizar suas funções, levando a filas de espera sem solução sistêmica disponível. Além disso, os profissionais de saúde não têm acesso aos prontuários completos, o que pode comprometer a qualidade do atendimento médico.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -683,7 +678,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Problemas com Exames Médicos Periódicos no SIAPENET</t>
+          <t>Problemas de Integração entre Saúde e SIAPENET</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -691,12 +686,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o sistema de exames médicos periódicos, incluindo dificuldades na realização de convocações, emissão de guias e atestados, além de problemas de acesso ao sistema e inconsistências nos registros. Os usuários relatam dificuldade em agendar perícia, emitir guias e atestados, e também problemas de acesso ao sistema, incluindo tela bloqueada e impossibilidade de preencher formulário anamnese. Além disso, há relatos de problemas com a emissão de guias e atestados, incluindo repetição de guias e emissão incompleta.</t>
+          <t>A integração entre o sistema de saúde e o SIAPENET está apresentando problemas, impedindo que os exames médicos periódicos sejam realizados corretamente. Isso inclui dificuldades em acessar guias de exame, emissão de atestados, agendamento de consultas e avaliações clínicas. Além disso, há problemas com a validação de guias de exame, código hexadecimal e status dos exames periódicos.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>O problema afeta a realização de exames médicos periódicos, levando a atrasos e dificuldades na prestação de serviços à população. Além disso, os problemas de acesso ao sistema e inconsistências nos registros podem levar a erros e imprecisões em dados importantes para a saúde pública.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -712,7 +707,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Problemas de Licenças em SIAPENET para Tratamento Médico</t>
+          <t>Falhas na Sincronização entre Afastamentos no SIAPE e SIASS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -720,13 +715,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado às dificuldades e problemas enfrentados pelos servidores públicos brasileiros em relação à concessão de licenças, especialmente para tratamento de saúde e acompanhamento familiar. Os principais temas abordados incluem a necessidade de agendar perícias médicas, a impossibilidade de cancelar ou prorrogar licenças, problemas com o sistema de cadastro de dependentes e a falta de orientação sobre procedimentos administrativos.
-Os servidores relatam dificuldades em agendar perícias médicas para tratamento de saúde, especialmente quando se trata de acompanhamento familiar. Além disso, há relatos de problemas com o sistema de licenças, incluindo a impossibilidade de cancelar ou prorrogar licenças, e a falta de orientação sobre procedimentos administrativos.</t>
+          <t>A falha na integração entre os sistemas SIAPE e SIASS impede que afastamentos registrados em um sistema sejam refletidos automaticamente no outro, causando problemas de sincronização de dados e dificultando a gestão de licenças e afastamentos. O problema se manifesta tanto em afastamentos recentes quanto em registros antigos que já deveriam ter sido sincronizados.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>A falta de agilidade no processo de concessão de licenças e a dificuldade em agendar perícias médicas podem levar a uma sobrecarga de trabalho para os servidores, que precisam lidar com as demandas dos usuários e também com as questões administrativas. Além disso, a falta de orientação sobre procedimentos administrativos pode levar a erros e atrasos no processo, o que pode afetar negativamente a qualidade do atendimento aos usuários.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -742,7 +736,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Cálculo e Integração de Benefícios Previdenciários</t>
+          <t>Falhas na Integração SIAPE-SIASS Afetam Proventos e Benefícios</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -750,12 +744,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas e dúvidas sobre aposentadoria, pensão e benefícios previdenciários. Os usuários estão tentando entender como calcular e solicitar aposentadoria, rever valores e proventos, e também estão enfrentando problemas com o sistema para realizar esses procedimentos. Alguns exemplos incluem dificuldades em calcular aposentadoria, divergências nos cálculos de proventos, problemas com a integração de dados e alterações de benefícios. Os usuários também estão solicitando orientação sobre como atualizar informações e realizar ajustes no sistema para garantir que os benefícios sejam calculados corretamente.</t>
+          <t>A falha na integração entre os sistemas de aposentadoria e previdência social (SIAPE e SIASS) está impedindo que as informações sejam sincronizadas corretamente, resultando em divergências nos cálculos de proventos e benefícios. Isso afeta tanto os afastamentos recentes quanto os registros antigos, exigindo intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>O problema operacional é que os servidores estão enfrentando dificuldades em calcular e solicitar aposentadoria, o que está causando atrasos e problemas para os usuários. Além disso, as divergências nos cálculos de proventos estão afetando a precisão dos benefícios previdenciários, o que pode levar a problemas financeiros para os beneficiários.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -771,7 +765,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Vinculação de Matrículas em SIASS</t>
+          <t>Problemas Recorrentes na Gestão de Dados Pessoais no SIAPE</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -779,20 +773,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas e solicitações de alterações nos sistemas de gestão de pessoal, benefícios e cargos dos órgãos públicos. As principais questões incluem:
-* Problemas com a vinculação de matrículas e CPFs;
-* Solicitações de inclusão de feriados municipais e estaduais no sistema;
-* Alterações em cargos, funções e benefícios;
-* Problemas com a progressão funcional e promoção de funcionários;
-* Solicitações de exclusão de cota parte e desconto de contribuições previdenciárias;
-* Problemas com a homologação de fichas de frequência e substituição de chefias;
-* Alterações em rubricas e pagamentos.
-Esses problemas afetam unidades SIASS de diferentes órgãos e se manifestam tanto em perícias agendadas incorretamente quanto em perícias antigas que deveriam ter sido encerradas mas permaneceram abertas no sistema. Em alguns casos, a perícia ativa pertence a outro órgão após remoção do servidor, impossibilitando qualquer ação pela unidade atual.</t>
+          <t>A integração entre sistemas e a gestão de dados pessoais é um problema recorrente. Muitos funcionários têm matrículas vinculadas a diferentes órgãos, o que gera inconsistências nos registros de licença médica e atrasa o processamento da folha de pagamento. Além disso, há problemas com a homologação de fichas de frequência, afastamentos e progressões funcionais, bem como com a inclusão de feriados municipais e estaduais nos calendários de trabalho.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Servidores ficam sem atendimento pericial, perícias anteriores incorretas não podem ser corrigidas e unidades acumulam filas de espera sem solução sistêmica disponível.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -808,7 +794,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Cadastro de Agências Itaú em Sistemas de Pagamento</t>
+          <t>Falhas na Integração Pagamentos Itaú Atrasam Folha de Pagamento</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -816,12 +802,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas de cadastro e inclusão de agências bancárias em sistemas de pagamento, especialmente no que diz respeito à Itaú. Os usuários estão solicitando a inclusão ou alteração de agências bancárias para realizar pagamentos, recebimento de salários, entre outros serviços financeiros. O problema é observado em diferentes órgãos e unidades, com alguns casos apresentando inconsistências nos dados bancários ou problemas de digitação de códigos. Alguns usuários também relatam dificuldades em encontrar a agência correta para realizar o cadastro.</t>
+          <t>A falha na integração entre os sistemas de pagamento e as agências bancárias, especialmente do Itaú, impede que os afastamentos sejam registrados automaticamente. Isso ocorre tanto em registros recentes quanto em antigos, exigindo intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>A falta de inclusão ou alteração de agências bancárias pode causar atrasos e impossibilidade de realização de pagamentos, recebimento de salários e outros serviços financeiros. Isso pode afetar negativamente as operações dos órgãos e unidades que dependem desses sistemas para realizar suas atividades.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -837,7 +823,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Reconhecimento de Titulações Docentes em SIPE</t>
+          <t>Cursos de Pós-Graduação Faltam em Registros do SIAPE</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -845,12 +831,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante é a necessidade de cadastramento e inclusão de cursos, formação e qualificação de professores em diferentes níveis (mestrado, doutorado, etc.) e áreas de estudo. Isso inclui solicitações para reconhecimento de titulações, inclusão de cargos e vagas, e ajustes nos padrões de classe e cargo. Além disso, há também solicitações para alterações em relação a carga horária, jornada de trabalho e remuneração de professores.</t>
+          <t>O padrão dominante nesse cluster de tickets é a necessidade de cadastramento e inclusão de cursos, formação e qualificação de professores em diferentes áreas do conhecimento. Os usuários solicitam a criação de registros para cursos de pós-graduação, mestrado, doutorado e especialização em diversas disciplinas, como educação, ciências sociais, saúde, tecnologia e engenharia. Além disso, há também solicitações de alterações em cargos, vagas e classes de professores, bem como a necessidade de inclusão de abonos e outros benefícios para os funcionários.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>A falta de cadastramento e reconhecimento de cursos e formação pode impedir que professores sejam contratados ou promovidos, afetando a capacidade da instituição em oferecer educação de qualidade. Além disso, a ausência de ajustes nos padrões de classe e cargo pode levar a problemas de remuneração e benefícios para os professores.</t>
+          <t>A falta de cadastramento desses cursos e formação pode causar problemas na gestão de carreiras dos professores, dificultando a avaliação de suas qualificações e habilidades. Além disso, a ausência de registros precisos pode afetar a concessão de benefícios e incentivos para os funcionários, gerando ineficiências no processo administrativo da instituição.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -866,7 +852,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Pagamentos e Cálculos em Folhas de Pagamento</t>
+          <t>Problemas de Cálculo de Benefícios e Descontos na Folha</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -874,12 +860,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o pagamento e cálculo de benefícios, gratificações e descontos em folhas de pagamento. Os usuários relatam dificuldades para realizar pagamentos, calcular valores corretos, e identificar erros em descontos indevidos. Alguns casos mencionam a necessidade de reajustes, correção de valores e supressão de descontos incorretos. O problema afeta unidades de diferentes órgãos e se manifesta tanto em pagamentos atuais quanto em períodos anteriores.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o pagamento e cálculo de benefícios, gratificações e descontos em folhas de pagamento. Os usuários estão relatando dificuldades para calcular e pagar corretamente esses valores, incluindo descontos indevidos, pagamentos atrasados e inconsistências nos registros de remuneração. Alguns exemplos incluem problemas com a inclusão de rubricas, cálculo de imposto de renda, desconto de benefícios e gratificações, além de questões relacionadas à folha de pagamento em geral.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Os problemas com o pagamento e cálculo de benefícios, gratificações e descontos podem causar atrasos no pagamento dos funcionários, acumulação de dívidas e impactar negativamente a gestão financeira das unidades.</t>
+          <t>As unidades precisam realizar ajustes manuais nos registros de remuneração para corrigir os erros, o que pode gerar atrasos no processamento da folha de pagamento e causar inconsistências nos registros de licença médica. Além disso, as unidades precisam lançar afastamentos manualmente em duplicidade, gerando mais trabalho e potencializando erros.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -895,7 +881,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Liberações de Rubricas VPNI em Instituidores</t>
+          <t>Problemas na Liberação de Rubricas VPNI para Instituidores</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -903,12 +889,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante é a solicitação de liberação de rubricas VPNI para instituidores, com destaque para a repetição constante da frase "solicito liberar rubrica vpni instituidor [nome] tendo vista alteracao tipo pensao paridade tipo pensao paridade". Isso sugere que há um problema recorrente no sistema de liberação de rubricas VPNI, que está impedindo a liberação das mesmas para os instituidores. Além disso, a presença da palavra "alteracao" e a repetição de "tipo pensao paridade" sugerem que o problema está relacionado à alteração do tipo de pensão ou paridade.</t>
+          <t>A solicitação de liberação de rubricas VPNI para instituidores, com a maioria dos casos apresentando problemas de alteração do tipo de pensão e paridade. Os usuários estão solicitando a liberação das rubricas VPNI para os instituidores, mas há uma falha na integração entre o sistema e a alteração do tipo de pensão e paridade, resultando em atrasos e inconsistências nos registros.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>A liberação das rubricas VPNI é necessária para que os instituidores possam receber as respectivas verbas, o que pode causar atrasos e problemas financeiros para eles. Além disso, a repetição constante da solicitação sugere que há um problema sistêmico que não está sendo resolvido, o que pode afetar a eficiência do processo de liberação das rubricas VPNI.</t>
+          <t>As unidades precisam lançar as rubricas VPNI manualmente, gerando atrasos no processamento da folha de pagamento e inconsistências nos registros de licença médica.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -924,7 +910,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Liberações de Matrícula em SIASS</t>
+          <t>Liberações de Matrícula para Funcionários com Critérios Específicos</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -932,12 +918,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante é a solicitação de liberação de matrícula, com repetição constante da frase "solicitamos liberacao matricula acima digitacao dados abaixo face [algum tipo de atendimento/diligência] seq". Isso sugere que há um problema no sistema de matrículas, onde as solicitações estão sendo rejeitadas ou não estão sendo processadas corretamente. Além disso, a presença da palavra "seq" em muitos dos chamados sugere que o problema está relacionado à sequência ou ordem das operações no sistema.</t>
+          <t>O padrão dominante é a solicitação de liberação de matrícula, com especificação de dados e condições específicas. A maioria dos chamados refere-se à necessidade de liberar matrículas para funcionários que atendem a certos critérios, como progressão funcional, aceleração ou concessão de adicional. Alguns chamados também solicitam a criação de vagas ou a transformação de vagas conforme anexo.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>A liberação de matrícula é necessária para que os servidores possam realizar suas funções e atender às demandas dos usuários, mas a repetição constante da solicitação sugere que há um problema sistêmico que está impedindo a liberação das matrículas. Isso pode causar atrasos e dificuldades para os servidores em realizar suas tarefas, afetando negativamente o atendimento aos usuários.</t>
+          <t>A falta de liberação de matrícula para funcionários que atendem aos critérios específicos pode causar atrasos no processamento da folha de pagamento e gerar inconsistências nos registros de licença médica. Além disso, a necessidade de liberar matrículas manualmente pode exigir intervenção da equipe de suporte, sobrecarregando os recursos disponíveis.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -953,7 +939,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Problemas com Gestão de Vagas em SIASS</t>
+          <t>Falhas na Integração de Vagas e Cargos no SIAPE</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -961,22 +947,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é a ocorrência de erros e inconsistências no sistema, especialmente relacionados à gestão de vagas, registros de frequência, progressões funcionais e redistribuição de cargos. Os usuários relatam problemas ao tentar realizar procedimentos como registro de faltas justificadas, inclusão de novos cadastros, alteração de lotações e efetivação de transferências. Alguns exemplos incluem:
-*   Erros ao tentar registrar frequência ou progressões funcionais;
-*   Problemas com a redistribuição de cargos e vagas;
-*   Inconsistências em registros de faltas justificadas;
-*   Erros ao tentar alterar lotações ou efetuar transferências.
-Esses problemas afetam unidades SIASS de diferentes órgãos, manifestando-se tanto em procedimentos agendados incorretamente quanto em procedimentos antigos que deveriam ter sido encerrados mas permaneceram abertos no sistema. Em alguns casos, a perícia ativa pertence a outro órgão após remoção do servidor, impossibilitando qualquer ação pela unidade atual.</t>
+          <t>O padrão dominante nesse cluster de tickets é a falha na integração entre sistemas, especificamente com relação à gestão de vagas e cargos. Muitos dos tickets relatam problemas ao tentar realizar alterações ou inclusões em sistemas como SIAPE, SIASS, PCA, etc., resultando em erros, inconsistências e impossibilidade de atualização de dados. Alguns exemplos incluem a falha na sincronização de afastamentos entre sistemas, problemas com a inclusão de cargos, vagas e registros de frequência, além da dificuldade em realizar alterações em lotações e exercícios.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Os erros e inconsistências no sistema impedem o funcionamento correto das unidades SIASS, causando atrasos na resolução de problemas e impactando negativamente a produtividade dos servidores. Além disso, os usuários não conseguem realizar procedimentos essenciais, como registro de frequência ou progressões funcionais, o que pode levar a consequências financeiras e administrativas.
-A frequência e urgência desses problemas parecem ser significativas, com muitos usuários relatando tentativas frustradas de resolver os erros e inconsistências. Alguns exemplos incluem:
-*   Muitos tickets relatam tentativas fracassadas de registrar frequência ou progressões funcionais;
-*   Algumas unidades SIASS relatam problemas persistentes com a redistribuição de cargos e vagas;
-*   Os usuários parecem estar aguardando respostas e soluções para os erros e inconsistências.
-Em resumo, o padrão dominante nesse cluster de tickets é a ocorrência de erros e inconsistências no sistema, especialmente relacionados à gestão de vagas, registros de frequência, progressões funcionais e redistribuição de cargos. Esses problemas afetam negativamente as unidades SIASS, causando atrasos na resolução de problemas e impactando negativamente a produtividade dos servidores.</t>
+          <t>A falta de integração eficaz entre os sistemas gera inconsistências nos registros de licença médica, atrasa o processamento da folha de pagamento e impede que as unidades realizem operações importantes, como alocação de vagas e cargos, exigindo intervenções manuais e gerando problemas administrativos.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -992,7 +968,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Problemas de Sincronização SIORG x EORG</t>
+          <t>Falhas na Sincronização SIORG-EORG Causam Inconsistências</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -1000,12 +976,13 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a estrutura organizacional (SIORG) e as unidades de gestão (UORG), incluindo erros, inconsistências e dificuldades em realizar alterações, cadastros e sincronizações entre esses sistemas. Os usuários relatam problemas ao tentar acessar ou manipular informações sobre unidades, cargos e funções, com mensagens de erro e falhas na comunicação entre os sistemas. Alguns exemplos incluem dificuldades em alterar a estrutura organizacional, erros ao tentar sincronizar informações entre SIORG e EORG, problemas ao criar novas UORGs ou unidades, e inconsistências nas informações registradas nos sistemas.</t>
+          <t>O padrão dominante nesse cluster de tickets é a falha na sincronização e integração entre os sistemas SIORG e EORG, que são responsáveis pela gestão de unidades organizacionais e estruturas hierárquicas. Isso está causando problemas em várias áreas, como a criação de novas UORGs, alteração de dados, inclusão de estagiários e funcionários, e até mesmo a geração de mensagens de erro e inconsistências nos registros.
+Essa falha é observada tanto em afastamentos recentes quanto em registros antigos que já deveriam ter sido sincronizados. Além disso, quando o servidor muda de lotação, o histórico de afastamentos do órgão anterior fica inacessível para a nova unidade, exigindo intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>A operação é afetada pela impossibilidade de realizar alterações e cadastros corretos, levando a erros e inconsistências na estrutura organizacional. Isso pode causar problemas em processos como gestão de pessoas, autorizações e pagamentos, além de dificultar a tomada de decisões baseadas em informações precisas.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr"/>
@@ -1021,7 +998,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Problemas de Auxílio Transporte no SISUP</t>
+          <t>Falhas na Sincronização Benefícios e Pagamento do Auxílio Transporte</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -1029,12 +1006,12 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas com o auxílio transporte, incluindo cancelamentos indevidos, descontos incorretos e dificuldades em solicitar novo benefício. Os usuários relatam que os sistemas de auxílio estão apresentando erros e inconsistências, impedindo-os de receber o benefício ou realizar alterações nos registros. Alguns casos mencionam a necessidade de cancelar o auxílio transporte anteriormente solicitado para poder solicitar um novo, enquanto outros relatam problemas com descontos automáticos que não estão sendo calculados corretamente. A situação parece ser generalizada e afeta várias unidades e órgãos.</t>
+          <t>A falha na integração entre o sistema de benefícios e o sistema de pagamento do auxílio transporte está impedindo que os beneficiários recebam o valor correto, gerando descontos indevidos e atrasos no processamento da folha de pagamento. O problema se manifesta tanto em afastamentos recentes quanto em registros antigos que já deveriam ter sido sincronizados. Quando o servidor muda de lotação, o histórico de afastamentos do órgão anterior fica inacessível para a nova unidade, exigindo intervenção manual da equipe de suporte para cada caso.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Os servidores ficam sem atendimento pericial, as folhas de pagamento são afetadas e os usuários acumulam filas de espera sem solução sistêmica disponível.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1050,7 +1027,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Problemas de Acesso a Fichas de Frequência no SISUP</t>
+          <t>Problemas de Registros de Frequência e Afastamentos no SIPEG</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -1058,12 +1035,12 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a frequência e afastamentos dos funcionários, incluindo dificuldades para registrar horas trabalhadas, licenças e afastamentos. Os usuários relatam problemas para acessar as fichas de frequência, homologar horas trabalhadas e registrar afastamentos. Alguns tickets também mencionam problemas com a compatibilidade entre os sistemas e a necessidade de criar novos códigos para afastamentos específicos. Em alguns casos, os usuários relatam que suas chefias imediatas conseguem enxergar as frequências dos funcionários, mas eles próprios não têm acesso.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a frequência e afastamentos dos funcionários, incluindo dificuldades para registrar horas trabalhadas, licenças e afastamentos. Os usuários relatam problemas para acessar as fichas de frequência, registrar pontos e horas trabalhadas, e também enfrentam dificuldades para incluir ocorrencias de afastamento, como licença maternidade ou paternidade. Além disso, há relatos de problemas com a homologação de frequência e afastamentos, o que impede a contabilização correta das horas trabalhadas.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>A falta de registro correto de horas trabalhadas e licenças está impedindo a homologação de processos e afastamentos, resultando em filas de espera sem solução sistêmica disponível. Além disso, os funcionários estão sendo prejudicados por não poderem acessar suas fichas de frequência e registrar seus afastamentos corretamente.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
@@ -1079,7 +1056,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Problemas de Cálculo de Contribuições Previdenciárias no SISUP</t>
+          <t>Falhas na Sincronização SIASS-SIAPE Atrasam Pagamentos</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
@@ -1087,12 +1064,12 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o cálculo e desconto de contribuições previdenciárias, especialmente no que diz respeito à Funpresp (Fundo de Previdência dos Servidores Públicos). Os usuários relatam dificuldades em calcular os valores corretos para descontar das folhas de pagamento, bem como problemas com a adesão e exclusão de contribuições. Alguns casos também mencionam decisões judiciais que determinaram a inclusão ou exclusão de certas rubricas de desconto. Há uma variedade de situações específicas, incluindo trocas de órgãos, mudanças em cargos e vínculos laborais, que afetam as contribuições previdenciárias dos servidores públicos.</t>
+          <t>A falha na integração entre o sistema de folha de pagamento (SIAPE) e o sistema de previdência complementar (SIASS) impede que os descontos da contribuição previdenciária sejam realizados automaticamente, resultando em inconsistências nos registros de licença médica e atraso no processamento da folha de pagamento. O problema afeta tanto os afastamentos recentes quanto os registros antigos que já deveriam ter sido sincronizados.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>A falta de cálculo correto das contribuições previdenciárias pode levar a descontos incorretos nas folhas de pagamento, causando problemas financeiros para os servidores e dificultando o gerenciamento orçamentário por parte dos órgãos. Além disso, decisões judiciais que determinam alterações nos descontos podem exigir ajustes significativos no sistema de gestão de folhas de pagamento, afetando a eficiência operacional e potencialmente gerando custos adicionais para os órgãos envolvidos.</t>
+          <t>As unidades precisam lançar descontos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1108,7 +1085,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Problemas de Cálculo de Pensão Alimentícia no SISUP</t>
+          <t>Problemas com Cálculo da Pensão Alimentícia no SIPEG</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
@@ -1116,12 +1093,12 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o cálculo e desconto de pensões alimentícias no sistema. Os usuários relatam dificuldades em incluir, alterar ou excluir dados bancários, bem como problemas com o cálculo do valor da pensão alimentícia, levando a descontos incorretos ou ausência de descontos. Alguns casos também mencionam problemas com a inclusão de dependentes e a geração de contas correntes para recebimento das pensões. Os usuários solicitam orientação e correção dos erros, muitas vezes com anexos de documentos que comprovam as situações.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o cálculo e desconto da pensão alimentícia em folhas de pagamento. Os usuários relatam inconsistências no valor da pensão, descontos indevidos ou ausência de descontos, além de dificuldades para cadastrar ou alterar dados bancários dos beneficiários. Alguns casos também mencionam problemas com a parametrização do cálculo da pensão alimentícia e a necessidade de ajustes no módulo responsável por essa funcionalidade.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>O sistema apresenta problemas em calcular e descontar corretamente as pensões alimentícias, levando a descontos incorretos ou ausência de descontos, o que afeta os usuários e gera trabalho adicional para os operadores.</t>
+          <t>A falta de precisão nos cálculos e descontos da pensão alimentícia pode levar a inconsistências nos registros de folha de pagamento, gerando problemas para os funcionários que dependem dessas verbas para suas necessidades básicas. Além disso, a demora em resolver esses problemas pode causar estresse e insegurança financeira para os beneficiários, além de comprometer a eficiência do processo de folha de pagamento.</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
@@ -1137,7 +1114,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Problemas de Certificado Digital nos Sistemas de Saúde</t>
+          <t>Problemas de Certificado Digital no SIAPE/SIASS</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
@@ -1145,12 +1122,12 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>O padrão dominante é a dificuldade de realizar procedimentos e solicitações relacionadas ao certificado digital, incluindo problemas de reconhecimento facial, validação e acesso aos sistemas. Os usuários relatam erros e inconsistências no sistema, impossibilitando a realização de tarefas essenciais, como a emissão de certificados digitais, a inclusão de dependentes em planos de saúde e a atualização de cadastros. Além disso, há relatos de problemas com a validação facial, incluindo erros de reconhecimento e impossibilidade de realizar procedimentos.</t>
+          <t>O padrão dominante é a dificuldade de realizar procedimentos relacionados ao certificado digital, incluindo solicitações de renovação, validação e reconhecimento facial. Isso está associado à falha na integração entre sistemas, como SIAPE e SIASS, o que impede a sincronização de dados e causa problemas de acesso e autorização. Além disso, há também problemas com a validação de dados pessoais e a atualização de registros cadastrais.</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>A falta de acesso aos sistemas e a incapacidade de realizar procedimentos essenciais afetam negativamente a operação dos órgãos e autarquias, levando a filas de espera sem solução sistêmica disponível. Servidores ficam sem atendimento pericial, e as unidades acumulam demanda sem solução imediata. Além disso, há relatos de problemas com a validação facial, incluindo erros de reconhecimento e impossibilidade de realizar procedimentos, o que pode levar a fraudes e tentativas de fraude.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr"/>
@@ -1166,7 +1143,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Problemas de Frequência no Módulo SIASS</t>
+          <t>Problemas com Módulo de Frequência no SIAPE/SIASS</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1174,12 +1151,12 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado ao problema de frequência, onde os usuários estão enfrentando dificuldades para registrar pontos e homologar folhas de frequência. Isso inclui problemas com o sistema, como bloqueios, perda de acesso, e inconsistências nos registros. Além disso, há também questões sobre a implementação do módulo de frequência, incluindo a necessidade de cadastramento de órgãos e a criação de ocorrencias para regularização das fichas. Em alguns casos, os usuários estão tentando resolver problemas específicos, como a perda de acesso à frequência ou a impossibilidade de homologar folhas.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado à implementação e uso do módulo de frequência (frequencia) em diferentes órgãos da administração pública. Os usuários estão relatando problemas para registrar pontos, homologar folhas de ponto, acessar o sistema e realizar procedimentos relacionados ao módulo de frequência. Alguns exemplos incluem a falta de acesso ao sistema, problemas com a vinculação de códigos, registros incorretos e dificuldades em homologar fichas de frequência.</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>A falta de registro de pontos e homologação de folhas de frequência está afetando o funcionamento das unidades SIASS, pois os servidores não podem atender às necessidades dos usuários, e as fichas pendentes estão acumulando. Além disso, a inabilidade de regularizar as fichas está causando problemas financeiros para os estagiários que precisam gerar efeitos financeiros automaticamente.</t>
+          <t>A implementação do módulo de frequência está causando problemas operacionais significativos, incluindo atrasos na folha de pagamento, inconsistências nos registros de ponto e necessidade de intervenção manual da equipe de suporte para resolver cada caso. Isso está gerando estresse para os usuários e a equipe de suporte, além de afetar a eficiência do processo de registro de frequência.</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr"/>
@@ -1195,7 +1172,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Problemas de Feriados em Sistema de Pessoal</t>
+          <t>Feriados Municipais e Estaduais no SIAPE/SIASS</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
@@ -1203,12 +1180,12 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas com a inclusão ou exclusão de feriados municipais em sistemas de frequência e gerenciamento de pessoal. Os usuários relatam que os sistemas não estão registrando corretamente os feriados, o que está causando problemas para as unidades administrativas e funcionários. Alguns casos específicos incluem a inclusão de feriados estaduais indevidos, a exclusão de feriados municipais importantes ou a falta de atualização dos sistemas com as novas leis e regulamentações sobre feriados.</t>
+          <t>A principal preocupação expressa nos chamados é a inconsistência na inclusão de feriados municipais e estaduais no sistema de frequência. Muitos municípios têm leis específicas que estabelecem datas diferentes para feriados, o que pode causar problemas ao registrar pontos de frequência. Além disso, há casos em que os sistemas registram feriados indevidos ou não permitem a marcação de pontos em dias considerados feriados. Isso gera necessidade de intervenção manual e pode afetar a contagem de horas trabalhadas.</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>A falta de registro correto de feriados está causando problemas para os funcionários que não podem registrar suas frequências, o que pode afetar sua remuneração e benefícios. Além disso, as unidades administrativas estão acumulando filas de espera sem solução sistêmica disponível, o que pode afetar a produtividade e eficiência do trabalho.</t>
+          <t>A inconsistência na inclusão de feriados municipais e estaduais no sistema de frequência pode levar a erros na contagem de horas trabalhadas, gerando problemas para os funcionários que precisam registrar suas presenças e faltas. Além disso, a necessidade de intervenção manual para resolver esses problemas pode consumir tempo e recursos da equipe de suporte.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr"/>
@@ -1224,7 +1201,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Problemas de Homologação de Férias no Sistema de Pessoal</t>
+          <t>Problemas de Homologação de Férias no SIAPE/SIASS</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1232,14 +1209,12 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a homologação de férias e alterações de lotação, especialmente em relação à atribuição de funções e chefias. Muitos dos tickets mencionam que o sistema não está permitindo a homologação de férias ou está apresentando erros ao tentar fazer isso. Além disso, há também problemas com a atribuição de funções e chefias, com alguns funcionários tendo suas lotações alteradas sem consentimento ou sem que seja possível alterá-las no sistema.
-Há também uma variedade de tickets que mencionam problemas específicos relacionados à gestão de pessoas, como a impossibilidade de cadastrar cursos realizados em sistemas de curriculo e a necessidade de inclusão de empresas em relações de treinamento. Alguns dos tickets também mencionam problemas com a frequência e ponto de funcionários.</t>
+          <t>A falha na integração entre os sistemas de gestão de pessoal e a homologação de férias é o padrão dominante nesse cluster. Os usuários relatam que, apesar de terem feito as alterações necessárias no sistema, a homologação de férias não está sendo registrada corretamente ou está apresentando erros. Isso ocorre tanto em afastamentos recentes quanto em registros antigos que já deveriam ter sido sincronizados. Além disso, os usuários também relatam problemas com a visualização e programação de férias, incluindo a impossibilidade de homologar férias para estagiários e funcionários que mudaram de cargo ou unidade.</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>A homologação de férias é um processo crítico para as unidades administrativas, pois afeta diretamente o atendimento ao público e a gestão das equipes. O problema de não permitir a homologação de férias ou apresentar erros ao tentar fazê-lo pode levar a uma paralisação do trabalho e impactar negativamente a produtividade da unidade.
-Além disso, os problemas com a atribuição de funções e chefias podem causar confusão e desorganização nas equipes, afetando a qualidade do atendimento ao público e a eficiência da gestão.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento. Além disso, os usuários também relatam que a falha na integração entre os sistemas está causando problemas com a gestão de férias, incluindo a impossibilidade de homologar férias para certos funcionários e a necessidade de intervenção manual para cada caso.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr"/>
@@ -1255,7 +1230,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Problemas de Contabilização de Horas no SIASS</t>
+          <t>Problemas com Compensação de Horas no SIAPE/SIASS</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
@@ -1263,12 +1238,12 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o uso e compensação de horas trabalhadas, especialmente em relação ao recesso (férias) dos funcionários. Os usuários relatam dificuldades para registrar, compensar ou migrar horas trabalhadas, resultando em saldos negativos, impossibilidade de utilização de horas acumuladas e outros problemas relacionados à gestão de tempo trabalhado. O sistema parece ter inconsistências na contabilização de horas, levando a situações como saldo zerado ou negativo, mesmo após compensações feitas. Além disso, há relatos de dificuldade em homologar frequência e pontos eletrônicos, o que pode afetar a carga horária dos funcionários e a gestão das horas trabalhadas.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a compensação de horas, especialmente em relação ao recesso (férias). Os usuários estão relatando dificuldades para compensar horas trabalhadas durante o período de recesso, com saldo negativo persistente no sistema. Além disso, há também questões sobre a migração de horas entre diferentes bancos de horas e a impossibilidade de utilização de horas acumuladas. Os usuários estão solicitando orientação e correção para resolver esses problemas.</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>A operação é afetada pela impossibilidade de registro correto de horas trabalhadas, levando a problemas na compensação de férias, saldos negativos em contas de horas e dificuldade em gerenciar carga horária. Isso pode resultar em funcionários sem atendimento pericial, perícias anteriores incorretas não podendo ser corrigidas e unidades acumulando filas de espera sem solução sistêmica disponível.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr"/>
@@ -1284,7 +1259,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Acesso em SIASS de Órgãos Diversos</t>
+          <t>Falhas em Sistemas de Gestão de Recursos Humanos</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
@@ -1292,26 +1267,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é o problema de acesso e funcionamento dos sistemas de suporte, especialmente relacionados a certificados digitais, perícias médicas e outros processos administrativos. Os usuários relatam dificuldades em acessar os sistemas, realizar certificados digitais, agendar perícia médica, entre outros problemas. Alguns casos específicos incluem:
-* Problemas com certificados digitais, como não conseguir assinar requerimentos ou obter acesso a perfis lider;
-* Dificuldades em agendar perícia médica, com mensagens de erro e impossibilidade de cancelar ou alterar agendamentos;
-* Problemas com o sistema de folha de pagamento, incluindo erros ao fechar a folha integrador e não possuir eventos pagamentos trabalhadores;
-* Dificuldades em cadastrar acesso a perfis lider e realizar certificados digitais.
-O problema afeta unidades SIASS de diferentes órgãos e se manifesta tanto em processos agendados incorretamente quanto em processos antigos que deveriam ter sido encerrados mas permaneceram abertos no sistema. Em alguns casos, a perícia ativa pertence a outro órgão após remoção do servidor, impossibilitando qualquer ação pela unidade atual.</t>
+          <t>O padrão dominante nesse cluster é a falha em sistemas de gestão de recursos humanos e financeiros da administração pública brasileira, incluindo problemas de integração entre sistemas, erros de cadastro, dificuldades de acesso a certificados digitais e outros. Os usuários relatam problemas para realizar tarefas como lançar afastamentos, incluir estagiários, efetuar atualizações cadastrais, entre outras. Além disso, há relatos de inconsistências nos registros de licença médica e atrasos no processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Os problemas nos sistemas de suporte afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtividade do trabalho.
-Os problemas também afetam negativamente o funcionamento das unidades SIASS, impedindo que os servidores possam realizar suas funções e atender às necessidades dos usuários. Isso leva a filas de espera sem solução sistêmica disponível, impactando a eficiência e produtiv</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr"/>
@@ -1327,7 +1288,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Pagamento e Descontos em Folha de Pagamento</t>
+          <t>Problemas de Pagamento em Folhas de Pagamento</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
@@ -1335,12 +1296,18 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o pagamento e descontos em folhas de pagamento, incluindo erros de cálculo, diferenças em valores, descontos não realizados e problemas de cadastramento de agências bancárias. Os usuários relatam dificuldades para realizar pagamentos, calcular descontos corretamente e entender as regras de absorção de rubricas. Alguns casos também mencionam problemas com a inclusão de valores em contracheques e divergências entre relatórios de folha de pagamento.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o pagamento e descontos em folhas de pagamento, especialmente em relação à rubrica, valores e descontos. Os usuários estão relatando dificuldades para realizar pagamentos, descontos e ajustes nos sistemas de folha de pagamento, incluindo problemas com a integração entre os sistemas, erros de cálculo e inconsistências nos registros.
+Os tickets também mencionam questões específicas como:
+* Problemas com a rubrica e descontos em folhas de pagamento
+* Erros de cálculo e inconsistências nos registros
+* Dificuldades para realizar pagamentos e descontos
+* Problemas com a integração entre os sistemas
+* Questões relacionadas à absorção de rubricas e diferenças de vencimento</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Os problemas com o pagamento e descontos afetam negativamente os servidores, que não recebem seus salários corretamente, e também causam transtornos para as unidades administrativas, que precisam lidar com as consequências desses erros. Além disso, a falta de clareza sobre as regras de absorção de rubricas pode levar a decisões equivocadas em relação ao pagamento de descontos e outros benefícios.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento. Além disso, os problemas com a rubrica e descontos estão causando dificuldades para realizar pagamentos e ajustes nos sistemas de folha de pagamento, afetando a eficiência do processo de pagamento e gerando custos adicionais para as unidades.</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr"/>
@@ -1356,7 +1323,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Frequência em Órgãos Governamentais</t>
+          <t>Problemas de Frequência em Instituições Federais</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
@@ -1364,12 +1331,12 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante é relacionado a problemas de frequência, horas e contagem de ponto dos funcionários em diferentes órgãos do governo. Os usuários relatam dificuldades para registrar frequência, homologação de fichas de frequência, compensação de horas, alterações de carga horária e outros problemas relacionados à gestão de tempo e ponto dos funcionários. Alguns casos mencionam erros no sistema, impossibilidade de registro de frequência, falta de vinculação entre os órgãos e a necessidade de priorização da adesão ao módulo de frequência.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o sistema de frequência (frequência) em instituições federais, como universidades e ministérios. Os usuários estão enfrentando dificuldades para registrar horas trabalhadas, homologar afastamentos, acessar fichas de frequência e realizar compensações de saldo de horas. Alguns exemplos incluem erros de contagem de horas, problemas com a vinculação de matrículas e CPFs, e dificuldades para visualizar ou registrar frequência em sistemas específicos.</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>A operação é afetada pela impossibilidade de registro de frequência, homologação de fichas de frequência e compensação de horas, o que pode levar à falta de atendimento pericial, atrasos na folha de pagamento e prejuízos financeiros. Além disso, a sobrecarga de trabalho dos analistas técnicos e a necessidade de manutenção constante do sistema podem afetar a capacidade de atendimento às demandas institucionais.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento. Além disso, os problemas com o sistema de frequência estão causando prejuízos financeiros e dificultando a gestão de recursos humanos nas instituições afetadas.</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1385,7 +1352,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Eventos Rejeitados no SGI - Remuneração e Previdência Social</t>
+          <t>Falhas em Integração do ESOCIAL com SIASS</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
@@ -1393,12 +1360,16 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas de eventos rejeitados no sistema gerenciador integrador, especialmente em relação à remuneração e previdência social. Os usuários relatam que os eventos estão sendo rejeitados sem motivo claro, o que está impedindo a geração de folhas de pagamento e outros processos importantes. Alguns motivos específicos mencionados incluem erros de cadastro temporário, falta de informações complementares em XMLs, CPFs inválidos ou ausentes, e problemas com rubricas e descontos contributários.</t>
+          <t>A falha na integração entre o sistema de remuneração (esocial) e outros sistemas, como o SIASS, está impedindo que os eventos sejam processados corretamente. Isso resulta em rejeições de eventos, com motivos variados, incluindo erros de cadastro, inconsistências em rubricas e descontos, e problemas de validação XML. Alguns casos específicos incluem:
+*   Erros de cadastro temporário;
+*   Inconsistências em rubricas e descontos;
+*   Problemas de validação XML;
+*   Falhas na integração entre sistemas.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>A rejeição desses eventos está causando atrasos na geração de folhas de pagamento, impactando negativamente os servidores que dependem desses processos para realizar suas funções. Além disso, a falta de solução sistemática para esses problemas está gerando uma grande quantidade de chamados e reclamações, sobrecarregando os operadores e afetando a estabilidade do sistema como um todo.</t>
+          <t>A falha na integração está causando atrasos no processamento de remunerações, gerando inconsistências nos registros e impactando negativamente a estabilidade do sistema.</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1414,7 +1385,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Aposentadoria em Cálculos de Proventos</t>
+          <t>Problemas de Integração de Benefícios de Aposentadoria</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
@@ -1422,12 +1393,12 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas com a aposentadoria e pensão dos funcionários públicos, incluindo questões de cálculo, integração de dados, suspensão de benefícios e dificuldades em acessar informações. Os usuários relatam problemas ao tentar realizar simulações de aposentadoria, calcular proventos, alterar situações funcionais e regularizar situações de aposentadoria. Alguns casos também mencionam erros de cálculo de gratificações, divergências em valores e remunerações, e dificuldades em acessar dados bancários.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com a integração e processamento de benefícios de aposentadoria e pensão, incluindo erros na contagem de tempo de serviço, inconsistências nos registros de contribuição e descontos, e dificuldades em realizar simulações e cálculos para aposentadoria. Além disso, há também problemas com a exclusão de descontos consignados, alterações em rubricas e processamento de requisições de aposentadoria.</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>A operação do sistema está sendo afetada pela falta de precisão nos cálculos de proventos e gratificações, o que pode levar a benefícios incorretos ou ausência de benefícios para os funcionários. Além disso, a dificuldade em acessar informações e realizar simulações de aposentadoria está causando atraso na tomada de decisões sobre aposentadorias e pensões, impactando negativamente as unidades administrativas que dependem dessas informações para tomar suas decisões.</t>
+          <t>As unidades precisam realizar ajustes manuais nos registros de contribuição e descontos, o que gera inconsistências nos dados e atrasa o processamento da folha de pagamento. Além disso, os usuários enfrentam dificuldades em acessar informações e realizar simulações para aposentadoria, o que pode afetar a eficiência no atendimento aos beneficiários.</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1443,7 +1414,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Matrícula em Órgãos Governamentais - Digitação de Dados</t>
+          <t>Problemas de Liberação de Matrícula em Padrões Específicos</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
@@ -1451,12 +1422,12 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante é a solicitação de liberação de matrícula, com foco em problemas relacionados à digitação de dados e face (presumivelmente referindo-se a alguma forma de progressão ou promoção). A maioria dos chamados pede a liberação da matrícula "acima" da digitação de dados, o que sugere que há algum problema com a atualização ou processamento desses dados. Alguns chamados também mencionam a necessidade de atendimento e diligência por parte do CGU (Caixa Econômico Federal) ou TCU (Tribunal de Contas da União), sugerindo que esses órgãos estão envolvidos em algum processo relacionado à matrícula.</t>
+          <t>O padrão dominante é a solicitação de liberação de matrícula com critérios específicos, como "acima" e "abaixo", relacionados à progressão funcional ou capacitação. Os usuários solicitam a liberação de suas matrículas para que possam realizar certas ações, como fópags (folha de pagamento) ou atendimentos, com base em critérios como progressão meritória, aceleração, capacitação ou indicação do CGU. Além disso, há referências a problemas de digitação e dados, sugerindo que há dificuldades técnicas no sistema.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>A liberação das matrículas está sendo atrasada devido a problemas com a digitação de dados, o que está afetando negativamente os servidores e funcionários que dependem desses processos para realizar suas funções.</t>
+          <t>A liberação de matrículas com critérios específicos está sendo retardada, causando atrasos nos processamentos de folha de pagamento e atendimentos.</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1472,7 +1443,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Transferência de Cargos após Mudanças Legais em Dezembro</t>
+          <t>Falhas na Integração entre SIAPE e SIASS</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -1480,13 +1451,12 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é a solicitação de exclusão ou ajuste de cargos, principalmente relacionados à transferência de funcionários entre diferentes categorias (fiscal, auditor, engenheiro, etc.) após mudanças legais em dezembro. Os usuários solicitam a correção da situação, pois os registros do sistema não refletem as alterações efetivas nos cargos dos funcionários. Alguns casos também mencionam problemas de contagem e carreira, bem como solicitações de transferência de vagas desocupadas.</t>
+          <t>A falha na integração entre o sistema de gestão de pessoal (SIAPE) e o sistema de informações sobre aposentadoria e pensões (SIASS) está impedindo que os afastamentos registrados em um sistema sejam refletidos automaticamente no outro. Isso ocorre tanto com afastamentos recentes quanto com registros antigos que já deveriam ter sido sincronizados, resultando em inconsistências nos registros de licença médica e atraso no processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>A falta de atualização dos registros no sistema causa problemas para os servidores que precisam realizar a gestão correta das carreiras e cargos, além de afetar a contagem de funcionários em diferentes categorias. Isso pode levar a problemas de planejamento e orçamentação, bem como à necessidade de ajustes posteriores para garantir a regularidade dos registros.
-**Frequência e Urgência**: A frequência dessas solicitações é alta, com 30 chamados (NÚCLEO) e 15 chamados (PERIFERIA), o que sugere um problema recorrente no sistema. Além disso, a urgência é evidente, pois os usuários solicitam ajustes urgentes para evitar problemas futuros e garantir a regularidade dos registros.</t>
+          <t>As unidades precisam lançar afastamentos manualmente em duplicidade, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1502,7 +1472,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Rubricas em Remuneração e Benefícios</t>
+          <t>Problemas de Autorização em Rubricas de Pagamento</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
@@ -1510,13 +1480,12 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster é relacionado a problemas de inclusão e liberação de rubricas, especialmente em relação à pensão e paridade. Os usuários solicitam autorização para incluir ou liberar rubricas, frequentemente mencionando valores atrasados, medidas provisórias e leis específicas. Alguns casos também envolvem solicitações de descontos em folhas de pagamento e problemas com sequências de pagamentos. A presença de termos como "vpni", "instituidor" e "tipo pensão paridade" sugere que esses problemas estão relacionados a questões de remuneração e benefícios dos funcionários.</t>
+          <t>A principal preocupação expressa nos chamados é a necessidade de autorização para inclusão ou liberação de rubricas, especialmente em relação à pensão e ao tipo de paridade. Muitos dos chamados solicitam a liberação de rubricas VPNI (Valor da Pensão do INSS) com instituidores específicos, o que sugere uma necessidade de atualização ou alteração das informações de pagamento. Além disso, alguns chamados mencionam a medida provisória e a lei em vigor, sugerindo que há mudanças nas regras de pagamento que precisam ser implementadas.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>A inclusão ou liberação incorreta de rubricas pode causar atrasos nos pagamentos, impactando negativamente os funcionários que dependem desses valores. Além disso, a falta de autorização para descontos em folhas de pagamento pode levar a problemas financeiros e administrativos para as unidades.
-Nota: A análise foi feita com base na frequência e diversidade dos termos presentes nos chamados, bem como nas solicitações específicas feitas pelos usuários.</t>
+          <t>A falta de autorização para inclusão ou liberação de rubricas pode causar atrasos nos pagamentos dos funcionários, levando a inconsistências nos registros de folha de pagamento e impactando negativamente na gestão financeira da instituição.</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1532,7 +1501,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Cadastro de Qualificações no SGRH</t>
+          <t>Problemas de Cadastro de Formação em SGRH</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
@@ -1540,12 +1509,12 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o cadastro e inclusão de informações de formação, cursos e vagas em um sistema de gestão de recursos humanos. Os usuários estão solicitando a inclusão de suas qualificações, certificados e diplomas, bem como a criação de novas vagas e cargos. Além disso, há também solicitações para alterar situações de planos de participantes, vincular formação e especializações, e corrigir falhas em transações de cadastro.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado a problemas com o cadastro e inclusão de informações de formação, cursos e qualificações dos funcionários em sistemas de gestão de recursos humanos. Muitas das solicitações são para incluir certificados, diplomas ou outros documentos de formação, especialmente em áreas como neurociências, direito público, gestão de recursos humanos, engenharia mecanica e outras especializações. Além disso, há também pedidos para alterar situações de plano de participante no sistema Funpresp, corrigir falhas de transação, redistribuir vagas e criar novos códigos de vaga.</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>A operação do sistema está sendo afetada pela falta de atualização das informações de formação e vagas, o que está impedindo a realização de parcerias institucionais e a ampliação da abertura de novas unidades de ensino. Além disso, os usuários estão enfrentando dificuldades para cadastrar suas qualificações e incluir cursos em seus currículos, o que está afetando sua capacidade de participar de planos de benefícios e programas de formação.</t>
+          <t>A falta de atualização desses dados pode levar a inconsistências nos registros de licença médica e atrasar o processamento da folha de pagamento. Além disso, a impossibilidade de incluir certificados e diplomas em curriculos pode impedir que os funcionários tenham acesso a oportunidades de formação correspondentes às suas qualificações, afetando sua carreira profissional.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1561,7 +1530,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Problemas de Cancelamento do Auxílio-Transporte em Perícias Ativas</t>
+          <t>Problemas de Integração de Auxílio-Transporte na Folha de Pagamento</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
@@ -1569,12 +1538,12 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>O padrão dominante nesse cluster de tickets é relacionado ao problema de cancelamento do benefício de auxílio-transporte, que está impedindo a abertura de novas perícia e causando transtornos administrativos. Os usuários estão relatando dificuldades em cancelar o benefício, mesmo após deferimento, e alguns casos apresentam situações anormais, como perícias ativas pertencentes a outro órgão após remoção do servidor. Além disso, há relatos de descontos incorretos no contracheque, duplicidade de descontos e problemas com o lançamento manual do benefício.</t>
+          <t>O padrão dominante nesse cluster de tickets é relacionado ao problema de integração entre o benefício de auxílio-transporte e a folha de pagamento. Muitos usuários relatam que os descontos do auxílio-transporte não estão sendo realizados corretamente, resultando em duplicidade de descontos ou falta de desconto. Alguns também mencionam problemas com o cancelamento do benefício, onde apesar de solicitado, o status permanece como "cancelado" e não é possível realizar novas solicitações. Isso está afetando a folha de pagamento e causando transtornos administrativos.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>O cancelamento do benefício de auxílio-transporte está impedindo a abertura de novas perícia, causando filas de espera sem solução sistêmica disponível. Além disso, os servidores estão sendo afetados por perícias antigas que não foram encerradas corretamente no sistema.</t>
+          <t>As unidades precisam lançar os descontos do auxílio-transporte manualmente, gerando inconsistências nos registros de licença médica e atrasando o processamento da folha de pagamento.</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
